--- a/untranslated/downloads/data-excel/16.5.1.2.xlsx
+++ b/untranslated/downloads/data-excel/16.5.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E0C8D8-4FCF-4FEB-B656-5751C84F92D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -82,13 +83,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -155,49 +164,50 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{2FFCBEB4-76B2-4B1D-AA16-A85994523915}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -213,9 +223,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,9 +263,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -290,7 +300,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -325,7 +335,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -498,14 +508,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,17 +530,17 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="2"/>
@@ -543,306 +553,328 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>2014</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>2015</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>2016</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>2017</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>2018</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>2019</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>2020</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>2021</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="7">
         <v>2022</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="N4" s="16">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>378</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>336</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>351</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>234</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>342</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>242</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>200</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>295</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>370</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <v>413</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="N5" s="14">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>62</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>69</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>72</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>52</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>56</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>79</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>73</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>163</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>137</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="N6" s="14">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>323</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>278</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>286</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>196</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>297</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>210</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>174</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>268</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>314</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <v>311</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="N7" s="14">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>57</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>65</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>61</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>44</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>53</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>68</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>67</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <v>155</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>121</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <v>76</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="N8" s="14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>55</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>58</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>65</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>38</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>45</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>32</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>26</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>27</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>50</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <v>102</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="N9" s="14">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>5</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>4</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>11</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>8</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>3</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>11</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <v>6</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <v>8</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="11">
         <v>16</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="11">
         <v>15</v>
+      </c>
+      <c r="N10" s="15">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
